--- a/medford_laringostroboskopy.xlsx
+++ b/medford_laringostroboskopy.xlsx
@@ -2110,7 +2110,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Ларингостробоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS — всего 1 позиций.</t>
+          <t>Ларингостробоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_laringostroboskopy.xlsx
+++ b/medford_laringostroboskopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать ларингостробоскопы для клиники?</t>
+          <t>Что такое ларингостробоскоп?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Частота вспышки). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Ларингостробоскоп — прибор для детального исследования голосовых складок и гортани. Он работает на основе стробоскопического эффекта: вспышки света синхронизируются с частотой вибрации связок, и врач видит их движение в замедленном или «остановленном» режиме. Это позволяет заметить нарушения, невидимые при обычном осмотре.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Как работает ларингостробоскопия?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Микрофонный датчик (ларингофон) на горле пациента преобразует колебания голосовых связок в электрический сигнал. С ним синхронизируется источник стробоскопического света. Эндоскоп передаёт изображение на видеопроцессор и монитор, где движение связок видно замедленным или как «стоячая волна». Так оценивают вибраторную функцию складок.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Когда назначают ларингостробоскопию?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены ATMOS. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Метод назначают при стойкой осиплости и других нарушениях голоса, подозрении на узелки, полипы, кисты, парезы и рубцовые изменения, для контроля результатов фонохирургии и при профосмотрах певцов, дикторов, педагогов. Показания в каждом случае определяет врач по клинической картине.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Чем светодиодный источник лучше лампового?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Белые светодиоды медицинского класса дают яркое равномерное освещение без сильного нагрева, в отличие от устаревших ламп. Они стабильнее по цветопередаче и дольше служат, что важно для точной оценки состояния слизистой голосовых складок во время исследования.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какой диапазон частот вспышки нужен?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Диапазон рабочих частот определяет, с какими голосами работает прибор. ATMOS Strobo 21 LED охватывает 70–1000 Гц. Для стандартных задач часто упоминают область 40–250 Гц, а широкий диапазон важен при работе с высокими и низкими голосами. Выбор зависит от профиля пациентов.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Для чего назначают ларингоскоп?</t>
+          <t>Совместим ли стробоскоп с нашей стойкой?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Стробоскоп работает в связке с эндоскопом, видеопроцессором и монитором, поэтому совместимость с существующей эндоскопической стойкой проверяют заранее. Наличие адаптеров для подключения ларингоскопов и световодов расширяет совместимость. При дооснащении готового кабинета это ключевой момент подбора.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1226,6 +1226,82 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Можно ли использовать прибор для обычной ларингоскопии?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Да, если модель поддерживает режим непрерывного освещения. Тогда один прибор работает и в стробоскопическом режиме для оценки вибрации связок, и в режиме постоянного света для стандартной ларингоскопии. Наличие такого режима уточняют по характеристикам конкретной модели.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>laringostroboskopy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Нужно ли регистрационное удостоверение?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Да. Ларингостробоскоп — медицинское изделие, его применение в клинике в РФ требует действующего регистрационного удостоверения Росздравнадзора. Перед закупкой запросите документ на конкретную модель у поставщика и проверьте его актуальность для планируемого применения.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>laringostroboskopy</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2110,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Ларингостробоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов ATMOS.</t>
+          <t>Ларингостробоскопы — приборы для детального исследования голосовых складок и гортани на основе стробоскопического эффекта: вспышки света синхронизируются с частотой вибрации связок, и врач видит их колебания в замедленном или «остановленном» режиме. Это позволяет заметить нарушения, невидимые при обычной ларингоскопии. В каталоге представлен стробоскоп ATMOS Strobo 21 LED с частотой вспышки 70–1000 Гц. Прибор работает в связке с эндоскопом, видеопроцессором и монитором, а светодиодный источник даёт яркое равномерное освещение без сильного нагрева.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2678,7 +2754,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое ларингостробоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2968,7 +3044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3294,12 +3370,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите задачи диагностики</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается ларингостробоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Ларингостробоскопию применяют при стойкой осиплости, подозрении на узелки, полипы, кисты, парезы и рубцовые изменения, для контроля фонохирургического лечения и профосмотров певцов, дикторов и педагогов. Круг задач определяет требования к прибору и режимам исследования.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3339,12 +3415,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте совместимость со стойкой</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Стробоскоп работает в связке с эндоскопом, видеопроцессором и монитором. Убедитесь в совместимости с существующей эндоскопической стойкой и наличии адаптеров для подключения ларингоскопов и световодов. Совместимость проверяют до покупки, особенно при дооснащении готового кабинета.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3384,12 +3460,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Оцените диапазон частот вспышки</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Частота вспышки. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Диапазон рабочих частот определяет, с какими голосами сможет работать прибор. ATMOS Strobo 21 LED охватывает 70–1000 Гц. Широкий диапазон важен для работы с высокими и низкими голосами; для стандартных задач часто упоминают рабочий диапазон в области 40–250 Гц.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3429,12 +3505,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Выберите тип источника света</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: ATMOS.</t>
+          <t>Современные модели используют белые светодиоды медицинского класса — яркий равномерный свет без сильного нагрева, в отличие от устаревших ламп. Светодиодный источник дольше служит и стабильнее по цветопередаче, что важно для оценки состояния слизистой голосовых складок.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3474,12 +3550,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте наличие нужных режимов</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Полезны режимы «медленное движение» и «стоячая волна», а также непрерывное освещение для стандартной ларингоскопии на том же приборе. Ручное управление частотой вспышек и настройка сдвига фазы дают гибкость при исследовании разных пациентов.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3519,12 +3595,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Оцените документирование и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Цифровой видеовыход позволяет архивировать результаты и передавать данные в информационную систему клиники. Уточните наличие регистрационного удостоверения Росздравнадзора и доступность обслуживания источника света и оптического тракта для выбранной модели.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3574,7 +3650,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Ларингостробоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены ATMOS. При выборе обращают внимание на частота вспышки, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Ларингостробоскопию назначают, когда обычный осмотр гортани уже не отвечает на вопрос — при стойкой осиплости, подозрении на узелки или парез. Ключевое в приборе — синхронизация вспышки с колебаниями связок через ларингофон и достаточный диапазон частот вспышки. Светодиодный источник медицинского класса даёт ровный свет без перегрева, в отличие от устаревших ламп. И обязательно проверяю совместимость стробоскопа с уже используемой эндоскопической стойкой.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3858,13 +3934,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое ларингостробоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Ларингостробоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов ATMOS. Подберём вариант под задачи вашего отделения.</t>
+          <t>Ларингостробоскоп исследует голосовые складки на основе стробоскопического эффекта: вспышки света синхронизируются с частотой вибрации связок через микрофонный датчик (ларингофон), и врач видит их движение в замедленном или «стоячем» режиме. Метод выявляет узелки, полипы, кисты, парезы и рубцовые изменения на ранних стадиях, когда обычная ларингоскопия малоинформативна. В каталоге — стробоскоп ATMOS Strobo 21 LED с частотой вспышки 70–1000 Гц. При выборе учитывают совместимость со стойкой, диапазон частот и режим непрерывного освещения.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3901,13 +3977,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Принцип работы ларингостробоскопа</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Частота вспышки), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>В основе прибора — стробоскопический эффект: вспышки источника света с регулируемой частотой синхронизируются с колебаниями голосовых складок. Микрофонный датчик (ларингофон) на горле пациента преобразует вибрацию связок в электрический сигнал, задающий частоту вспышек. Эндоскоп с оптическим каналом передаёт изображение на видеопроцессор и монитор, где движение складок видно замедленным или неподвижным.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3944,13 +4020,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Из чего состоит прибор</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Ключевые компоненты ларингостробоскопа: источник стробоскопического света с регулируемой частотой вспышек (в современных моделях — белые светодиоды медицинского класса); микрофонный датчик-ларингофон; эндоскоп (жёсткий или гибкий) с оптическим каналом; видеопроцессор и монитор для отображения и записи. Цифровой видеовыход позволяет архивировать результаты и передавать их в информационную систему клиники.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3987,13 +4063,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>На что смотреть при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе учитывают совместимость с существующей эндоскопической стойкой, диапазон рабочих частот вспышек, наличие режима непрерывного освещения для стандартной ларингоскопии и удобство ручного управления частотой. Полезны режимы «медленное движение» и «стоячая волна», регулировка сдвига фазы и адаптеры для подключения ларингоскопов и световодов разных производителей.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4010,6 +4086,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Диагностические возможности метода</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Ларингостробоскопия выявляет функциональные и органические патологии гортани — узелки, полипы, кисты, парезы, рубцовые изменения — на ранних стадиях, когда рутинная ларингоскопия малоинформативна. Метод применяют при стойкой осиплости, для контроля результатов фонохирургического лечения и при профессиональных осмотрах певцов, дикторов и педагогов. Показания и трактовку результатов определяет врач.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>laringostroboskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
